--- a/stories/arbres/ATOM-REL.PAR.002-03.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Justine est au bac à sable. Maman est près d'elle. Un enfant a le seau rouge. Justine a envie du seau. Maman dit : on attend. L'autre finit. Puis c'est mon tour. Justine attend. Elle pose les mains sur ses genoux. Le sable est tiède. Elle écoute. L'autre verse le sable. Puis l'autre pose le seau. Maman dit : maintenant. Puis mon tour. Justine prend le seau. Elle le remplit. Le sable coule. Justine sourit. Elle a attendu. Puis c'est son tour. Maman dit : bravo. Justine répète : attendre. Puis mon tour.</t>
+          <t>Justine est au bac à sable. Maman est près d'elle. Un enfant a le seau rouge. Justine a envie du seau. On attend. L'autre finit. Puis c'est mon tour. Justine attend. Elle pose les mains sur ses genoux. Le sable est tiède. Elle écoute. L'autre verse le sable. Puis l'autre pose le seau. Maintenant. Puis mon tour. Justine prend le seau. Elle le remplit. Le sable coule. Justine sourit. Elle a attendu. Puis c'est son tour. Bravo. Justine répète : attendre. Puis mon tour.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Justine est au bac à sable. Maman est près d'elle. Un enfant a le seau rouge. Justine a envie du seau.
+maman|On attend. L'autre finit.
+narrateur|Puis c'est mon tour. Justine attend. Elle pose les mains sur ses genoux. Le sable est tiède. Elle écoute. L'autre verse le sable. Puis l'autre pose le seau.
+maman|Maintenant.
+narrateur|Puis mon tour. Justine prend le seau. Elle le remplit. Le sable coule. Justine sourit. Elle a attendu. Puis c'est son tour.
+maman|Bravo.
+narrateur|Justine répète : attendre. Puis mon tour.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Justine veut le seau. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Justine a attendu. Puis c'est son tour. Elle a pris le seau. Maman était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Justine pose le seau. Maman lui donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-03.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Justine répète : attendre. Puis mon tour.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Justine veut le seau. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Justine a attendu. Puis c'est son tour. Elle a pris le seau. Maman était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Justine pose le seau. Maman lui donne la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.PAR.002-03.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Justine attend le seau</t>
+          <t>Nina attend le seau</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>REL.PAR.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le sable est tiède. Chouchou a le seau rouge. Nina pose les mains sur ses genoux. Elle attend. Puis c'est son tour.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Justine est au bac à sable. Maman est près d'elle. Un enfant a le seau rouge. Justine a envie du seau. On attend. L'autre finit. Puis c'est mon tour. Justine attend. Elle pose les mains sur ses genoux. Le sable est tiède. Elle écoute. L'autre verse le sable. Puis l'autre pose le seau. Maintenant. Puis mon tour. Justine prend le seau. Elle le remplit. Le sable coule. Justine sourit. Elle a attendu. Puis c'est son tour. Bravo. Justine répète : attendre. Puis mon tour.</t>
+          <t>La barrière en bois est tiède. De petites fourmis marchent dessus. Le bois est lisse, un peu sec. Derrière la haie, une petite maison. Nina habite ici, avec maman. Papa arrose les fleurs, plus loin. Ça sent les fleurs, un peu. Un panier repose près de la haie. Dans le panier, une bouteille d'eau. Cet après-midi, le soleil est chaud. Le soleil chauffe le bac à sable. Le sable sent le pain chaud. Une pelle jaune dort au bord. Tu as vu le sable, Nina ? Il est tout jaune, maman. Viens. On va près du bac. En ce moment, Nina s'approche. Ses pieds touchent le sable tiède. Le sable coule entre les doigts. Chouchou a le seau rouge. Chouchou verse le sable, tout doux. Le seau fait un petit bruit. Nina a envie du seau. Maman, je veux le seau. On attend. L'autre finit. Puis c'est ton tour. Nina pose les mains sur ses genoux. Elle reste près de maman. Elle écoute le sable qui coule. Chouchou verse encore un peu. Nina attend. Tu attends bien, Nina. Tes pieds sont au sol. Bravo. Un oiseau chante dans la haie. Tu as entendu l'oiseau ? Oui, maman. Une coccinelle s'arrête sur une feuille. Elle est toute petite, hein ? Oui. Chouchou remplit encore le seau. Nina compte tout bas. Un. Deux. Trois. Le seau rouge brille. Nina attend encore. On reste près. Puis ce sera ton tour.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1329,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Justine est au bac à sable. Maman est près d'elle. Un enfant a le seau rouge. Justine a envie du seau.
-maman|On attend. L'autre finit.
-narrateur|Puis c'est mon tour. Justine attend. Elle pose les mains sur ses genoux. Le sable est tiède. Elle écoute. L'autre verse le sable. Puis l'autre pose le seau.
-maman|Maintenant.
-narrateur|Puis mon tour. Justine prend le seau. Elle le remplit. Le sable coule. Justine sourit. Elle a attendu. Puis c'est son tour.
+          <t>narrateur|La barrière en bois est tiède.
+narrateur|De petites fourmis marchent dessus.
+narrateur|Le bois est lisse, un peu sec.
+narrateur|Derrière la haie, une petite maison.
+narrateur|Nina habite ici, avec maman.
+narrateur|Papa arrose les fleurs, plus loin.
+narrateur|Ça sent les fleurs, un peu.
+narrateur|Un panier repose près de la haie.
+narrateur|Dans le panier, une bouteille d'eau.
+narrateur|Cet après-midi, le soleil est chaud.
+narrateur|Le soleil chauffe le bac à sable.
+narrateur|Le sable sent le pain chaud.
+narrateur|Une pelle jaune dort au bord.
+maman|Tu as vu le sable, Nina ?
+enfant-f|Il est tout jaune, maman.
+maman|Viens.
+maman|On va près du bac.
+narrateur|En ce moment, Nina s'approche.
+narrateur|Ses pieds touchent le sable tiède.
+narrateur|Le sable coule entre les doigts.
+narrateur|Chouchou a le seau rouge.
+narrateur|Chouchou verse le sable, tout doux.
+narrateur|Le seau fait un petit bruit.
+narrateur|Nina a envie du seau.
+enfant-f|Maman, je veux le seau.
+maman|On attend.
+maman|L'autre finit.
+maman|Puis c'est ton tour.
+narrateur|Nina pose les mains sur ses genoux.
+narrateur|Elle reste près de maman.
+narrateur|Elle écoute le sable qui coule.
+narrateur|Chouchou verse encore un peu.
+narrateur|Nina attend.
+maman|Tu attends bien, Nina.
+maman|Tes pieds sont au sol.
 maman|Bravo.
-narrateur|Justine répète : attendre. Puis mon tour.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Un oiseau chante dans la haie.
+maman|Tu as entendu l'oiseau ?
+enfant-f|Oui, maman.
+narrateur|Une coccinelle s'arrête sur une feuille.
+maman|Elle est toute petite, hein ?
+enfant-f|Oui.
+narrateur|Chouchou remplit encore le seau.
+narrateur|Nina compte tout bas.
+enfant-f|Un.
+enfant-f|Deux.
+enfant-f|Trois.
+narrateur|Le seau rouge brille.
+narrateur|Nina attend encore.
+maman|On reste près.
+maman|Puis ce sera ton tour.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>sable</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Justine veut le seau. Que fait-elle ?</t>
+          <t>Nina veut le seau. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1567,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Justine veut le seau. Que fait-elle ?</t>
+          <t>narrateur|Nina veut le seau.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Justine a attendu. Puis c'est son tour. Elle a pris le seau. Maman était là.</t>
+          <t>Nina attend encore un peu. Chouchou pose le seau. Maintenant. Puis c'est ton tour. Puis mon tour. Nina prend le seau rouge. Elle le remplit. Le sable coule, tout fin. Un grain reste sur le bord. Bravo, Nina. Tu as attendu. C'est du bon travail. Le sable est tiède, maman. Oui. Il est doux. Chouchou attend maintenant, tout près. Tu as su attendre. Nina tapote le seau, tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1740,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Justine a attendu. Puis c'est son tour. Elle a pris le seau. Maman était là.</t>
+          <t>narrateur|Nina attend encore un peu.
+narrateur|Chouchou pose le seau.
+maman|Maintenant.
+maman|Puis c'est ton tour.
+enfant-f|Puis mon tour.
+narrateur|Nina prend le seau rouge.
+narrateur|Elle le remplit.
+narrateur|Le sable coule, tout fin.
+narrateur|Un grain reste sur le bord.
+maman|Bravo, Nina.
+maman|Tu as attendu.
+maman|C'est du bon travail.
+enfant-f|Le sable est tiède, maman.
+maman|Oui.
+maman|Il est doux.
+narrateur|Chouchou attend maintenant, tout près.
+maman|Tu as su attendre.
+narrateur|Nina tapote le seau, tout doux.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Justine pose le seau. Maman lui donne la main.</t>
+          <t>Nina pose le seau près de Chouchou. Tu veux lui laisser le seau ? Oui, maman. Bravo. On peut prêter. Chouchou reprend le seau. Nina prend la main de maman. On reste encore un peu ? Oui. Le sable reste tiède. La pelle jaune attend. Tu as bien attendu, Nina. Puis c'était mon tour. Oui. Puis ton tour. Les fourmis marchent encore. On boit un peu d'eau ? Oui, maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1925,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Justine pose le seau. Maman lui donne la main.</t>
+          <t>narrateur|Nina pose le seau près de Chouchou.
+maman|Tu veux lui laisser le seau ?
+enfant-f|Oui, maman.
+maman|Bravo.
+maman|On peut prêter.
+narrateur|Chouchou reprend le seau.
+narrateur|Nina prend la main de maman.
+maman|On reste encore un peu ?
+enfant-f|Oui.
+narrateur|Le sable reste tiède.
+narrateur|La pelle jaune attend.
+maman|Tu as bien attendu, Nina.
+enfant-f|Puis c'était mon tour.
+maman|Oui.
+maman|Puis ton tour.
+narrateur|Les fourmis marchent encore.
+maman|On boit un peu d'eau ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1970,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis c'était mon tour. Bravo. Tu as fait du bon travail. Le seau rouge brille encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2110,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai attendu.
+enfant-f|Puis c'était mon tour.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le seau rouge brille encore.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2175,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-03.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-03.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Justine est au bac à sable. Maman est près d'elle. Un enfant a le seau rouge. Justine a envie du seau. Maman dit : on attend. L'autre finit. Puis c'est mon tour. Justine attend. Elle pose les mains sur ses genoux. Le sable est tiède. Elle écoute. L'autre verse le sable. Puis l'autre pose le seau. Maman dit : maintenant. Puis mon tour. Justine prend le seau. Elle le remplit. Le sable coule. Justine sourit. Elle a attendu. Puis c'est son tour. Maman dit : bravo. Justine répète : &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Puis mon tour.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La barrière en bois est tiède. De petites fourmis marchent dessus. Le bois est lisse, un peu sec. Derrière la haie, une petite maison. Nina habite ici, avec maman. Papa arrose les fleurs, plus loin. Ça sent les fleurs, un peu. Un panier repose près de la haie. Dans le panier, une bouteille d'eau. Cet après-midi, le soleil est chaud. Le soleil chauffe le bac à sable. Le sable sent le pain chaud. Une pelle jaune dort au bord. Tu as vu le sable, Nina ? Il est tout jaune, maman. Viens. On va près du bac. En ce moment, Nina s'approche. Ses pieds touchent le sable tiède. Le sable coule entre les doigts. Chouchou a le seau rouge. Chouchou verse le sable, tout doux. Le seau fait un petit bruit. Nina a envie du seau. Maman, je veux le seau. On attend. L'autre finit. Puis c'est ton tour. Nina pose les mains sur ses genoux. Elle reste près de maman. Elle écoute le sable qui coule. Chouchou verse encore un peu. Nina attend. Tu attends bien, Nina. Tes pieds sont au sol. Bravo. Un oiseau chante dans la haie. Tu as entendu l'oiseau ? Oui, maman. Une coccinelle s'arrête sur une feuille. Elle est toute petite, hein ? Oui. Chouchou remplit encore le seau. Nina compte tout bas. Un. Deux. Trois. Le seau rouge brille. Nina attend encore. On reste près. Puis ce sera ton tour.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Justine veut le seau. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina veut le seau. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1571,7 +1571,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1596,12 +1595,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina attend encore un peu. Chouchou pose le seau. Maintenant. Puis c'est ton tour. Puis mon tour. Nina prend le seau rouge. Elle le remplit. Le sable coule, tout fin. Un grain reste sur le bord. Bravo, Nina. Tu as attendu. C'est du bon travail. Le sable est tiède, maman. Oui. Il est doux. Chouchou attend maintenant, tout près. Tu as su attendre. Nina tapote le seau, tout doux.</t>
+          <t>Nina attend encore un peu. Chouchou pose le seau. Maintenant. Puis c'est ton tour. Puis mon tour. Nina prend le seau rouge. Elle le remplit. Le sable coule, tout fin. Un grain reste sur le bord. Bravo, Nina. Tu as attendu. Le sable est tiède, maman. Oui. Il est doux. Chouchou attend maintenant, tout près. Tu as su attendre. Nina tapote le seau, tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Justine a attendu. &lt;emphasis level="moderate"&gt;puis&lt;/emphasis&gt; c'est son tour. Elle a pris le seau. Maman était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina attend encore un peu. Chouchou pose le seau. Maintenant. Puis c'est ton tour. Puis mon tour. Nina prend le seau rouge. Elle le remplit. Le sable coule, tout fin. Un grain reste sur le bord. Bravo, Nina. Tu as attendu. Le sable est tiède, maman. Oui. Il est doux. Chouchou attend maintenant, tout près. Tu as su attendre. Nina tapote le seau, tout doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1751,7 +1750,6 @@
 narrateur|Un grain reste sur le bord.
 maman|Bravo, Nina.
 maman|Tu as attendu.
-maman|C'est du bon travail.
 enfant-f|Le sable est tiède, maman.
 maman|Oui.
 maman|Il est doux.
@@ -1760,7 +1758,6 @@
 narrateur|Nina tapote le seau, tout doux.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1790,7 +1787,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Justine pose le seau. Maman lui donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina pose le seau près de Chouchou. Tu veux lui laisser le seau ? Oui, maman. Bravo. On peut prêter. Chouchou reprend le seau. Nina prend la main de maman. On reste encore un peu ? Oui. Le sable reste tiède. La pelle jaune attend. Tu as bien attendu, Nina. Puis c'était mon tour. Oui. Puis ton tour. Les fourmis marchent encore. On boit un peu d'eau ? Oui, maman.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1945,7 +1942,6 @@
 enfant-f|Oui, maman.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1970,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai attendu. Puis c'était mon tour. Bravo. Tu as fait du bon travail. Le seau rouge brille encore. L'histoire est finie.</t>
+          <t>J'ai attendu. Puis c'était mon tour. Bravo. Le seau rouge brille encore.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai attendu. Puis c'était mon tour. Bravo. Le seau rouge brille encore.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2113,12 +2109,9 @@
           <t>enfant-f|J'ai attendu.
 enfant-f|Puis c'était mon tour.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le seau rouge brille encore.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le seau rouge brille encore.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2137,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2182,6 +2175,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-03.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-03.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Justine, maman</t>
+          <t>Nina, Chouchou, maman</t>
         </is>
       </c>
     </row>
